--- a/2022 data/excel_outputs/172_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/172_boothwise_data.xlsx
@@ -14,9 +14,87 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="128">
   <si>
     <t>AC 172 Booth-wise Data</t>
+  </si>
+  <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
   </si>
   <si>
     <t>BOOTH ID</t>
@@ -25,1255 +103,229 @@
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>#### ######## ##### ##### ######## #### ######.1</t>
+    <t>NAN</t>
   </si>
   <si>
-    <t>#### ######## ##### ##### ######## #### ######.2</t>
+    <t>SAR&amp;VATI 0SHASHU MI!DAR &lt;NARALA NAGAR K SAM YA-6</t>
   </si>
   <si>
-    <t>#### ######## ##### ##### ######## #### ######.3</t>
+    <t>NAN ROOM NO. 346</t>
   </si>
   <si>
-    <t>#### ######## ##### ##### ######## #### ######.4</t>
+    <t>NAN ROOM ROOM NO. 347</t>
   </si>
   <si>
-    <t>#### ######## ##### ##### ######## #### ######.5</t>
+    <t>NAN ROOM ROOM ROOM NO. 348</t>
   </si>
   <si>
-    <t>#### ######## ##### ##### ######## #### ######.6</t>
+    <t>NAN ROOM ROOM ROOM ROOM NO. 349</t>
   </si>
   <si>
-    <t>###### ###### ##### ######## #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM NO. 350</t>
   </si>
   <si>
-    <t>###### ###### ##### ######## #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM NO. 351</t>
   </si>
   <si>
-    <t>###### ###### ##### ######## #### ######.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 352</t>
   </si>
   <si>
-    <t>###### ###### ##### ######## #### ######.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 353</t>
   </si>
   <si>
-    <t>##### #### ##### ##### ##### ### #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 354</t>
   </si>
   <si>
-    <t>##### #### ##### ##### ##### ### #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 355</t>
   </si>
   <si>
-    <t>##### #### ##### ##### ##### ### #### ######.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 356</t>
   </si>
   <si>
-    <t>####### ######## ###### ##### ###### ######## #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 357</t>
   </si>
   <si>
-    <t>####### ######## ###### ##### ###### ######## #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 358</t>
   </si>
   <si>
-    <t>####### ######## ###### ##### ###### ######## #### ######.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 359</t>
   </si>
   <si>
-    <t>####### ######## ###### ##### ###### ######## #### ######.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 360</t>
   </si>
   <si>
-    <t>####### ######## ###### ##### ###### ######## #### ######.5</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 361</t>
   </si>
   <si>
-    <t>####### ######## ###### ##### ###### ######## #### ######.6</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 362</t>
   </si>
   <si>
-    <t>####### ######## ###### ##### ###### ######## #### ######.7</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 363</t>
   </si>
   <si>
-    <t>####0 ##0 ######### #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 364</t>
   </si>
   <si>
-    <t>####0 ##0 ######### #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 365</t>
   </si>
   <si>
-    <t>####0 ##0 ######### #### ######.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 366</t>
   </si>
   <si>
-    <t>####0 ##0 ######### #### ######.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 367</t>
   </si>
   <si>
-    <t>####0 ##0 ######### #### ######.5</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
   </si>
   <si>
-    <t>####0 ##0 ######### #### ######.6</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
   </si>
   <si>
-    <t>##### ######## ##### ######## ######### #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
   </si>
   <si>
-    <t>##### ######## ##### ######## ######### #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
   </si>
   <si>
-    <t>##### ######## ##### #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
   </si>
   <si>
-    <t>##0##0##0 ###### ######### #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
   </si>
   <si>
-    <t>##0##0##0 ###### ######### #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
   </si>
   <si>
-    <t>##0##0##0 ###### ######### #### ######.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
   </si>
   <si>
-    <t>##0##0##0 ###### ######### #### ######.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
   </si>
   <si>
-    <t>##0##0##0 ###### ######### #### ######.5</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
   </si>
   <si>
-    <t>##0##0##0 ###### ######### #### ######.6</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
   </si>
   <si>
-    <t>##0##0##0 ###### ######### #### ######.7</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
   </si>
   <si>
-    <t>##0##0##0 ###### ######### #### ######.8</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
   </si>
   <si>
-    <t>######### ###### #### ######### #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
   </si>
   <si>
-    <t>######### ###### #### ######### #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
   </si>
   <si>
-    <t>######### ###### #### ######### #### ######.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
   </si>
   <si>
-    <t>######### ###### #### ######### #### ######.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
   </si>
   <si>
-    <t>######### ###### #### ######### #### ######.5</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
   </si>
   <si>
-    <t>######### ###### #### ######### #### ######.6</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
   </si>
   <si>
-    <t>##### ######## ### 6 ###### ## ##### ######### #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
   </si>
   <si>
-    <t>##### ######## ### 6 ###### ## ##### ######### #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
   </si>
   <si>
-    <t>##### ######## ### 6 ###### ## ##### ######### #### ######.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
   </si>
   <si>
-    <t>##### ######## ### 6 ###### ## ##### ######### #### ######.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
   </si>
   <si>
-    <t>####0 ##0 ##### ### ### #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
   </si>
   <si>
-    <t>####0 ##0 ##### ### ### #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
   </si>
   <si>
-    <t>####0 ##0 ##### ### ### #### ######.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 393</t>
   </si>
   <si>
-    <t>####### ##### ######### ##### ##### #### ###### #### #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 394</t>
   </si>
   <si>
-    <t>####### ##### ######### ##### ##### #### ###### #### #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 395</t>
   </si>
   <si>
-    <t>####### ##### ######### ##### ##### #### ###### #### #### ######.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 396</t>
   </si>
   <si>
-    <t>###### ###### ##### ##### ######## ### #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
   </si>
   <si>
-    <t>###### ###### ##### ##### ######## ### #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
   </si>
   <si>
-    <t>###### ###### ##### ##### ######## ### #### ######.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
   </si>
   <si>
-    <t>###### ###### ##### ##### ######## ### #### ######.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
   </si>
   <si>
-    <t>###### ###### ##### ##### ######## ### #### ######.5</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
   </si>
   <si>
-    <t>###### ###### ##### ##### ######## ### #### ######.6</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
   </si>
   <si>
-    <t>###### ###### ##### ##### ######## ### #### ######.7</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
   </si>
   <si>
-    <t>###### ###### ##### ##### ######## ### #### ######.8</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
   </si>
   <si>
-    <t>###### ###### ##### ##### ######## ### #### ######.9</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
   </si>
   <si>
-    <t>#### ####### ##### ##### ######## ### #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
   </si>
   <si>
-    <t>#### ####### ##### ##### ######## ### #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
   </si>
   <si>
-    <t>######### ###### ##### ##### ######### #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
   </si>
   <si>
-    <t>######### ###### ##### ##### ######### #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
   </si>
   <si>
-    <t>######### ###### ##### ##### ######### #### ######.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
   </si>
   <si>
-    <t>######### ###### ##### ##### ######### #### ######.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
   </si>
   <si>
-    <t>#### ### ##### ##### #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
   </si>
   <si>
-    <t>#### ### ##### ##### #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
   </si>
   <si>
-    <t>#### ### ##### ##### #### ######.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
   </si>
   <si>
-    <t>####0 ######## ####### #### #### ### #### ######.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
   </si>
   <si>
-    <t>####0 ######## ####### #### #### ### #### ######.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
   </si>
   <si>
-    <t>####0 ######## ####### #### #### ### #### ######.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
   </si>
   <si>
-    <t>####### ## ######### ##### ####### ####### #### ######.1</t>
-  </si>
-  <si>
-    <t>####### ## ######### ##### ####### ####### #### ######.2</t>
-  </si>
-  <si>
-    <t>####### ## ######### ##### ####### ####### #### ######.3</t>
-  </si>
-  <si>
-    <t>####### ## ######### ##### ####### ####### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ##### ### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ##### ### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ##### ### #### ######.3</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ### #### ######.1</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ### #### ######.2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ### #### ######.3</t>
-  </si>
-  <si>
-    <t>####### ####### ## ### ##### ######## #### ######.1</t>
-  </si>
-  <si>
-    <t>####### ####### ## ### ##### ######## #### ######.2</t>
-  </si>
-  <si>
-    <t>####### ####### ## ### ##### ######## #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ### ##0 ##### #### ###### ### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ### ##0 ##### #### ###### ### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ### ##0 ##### #### ###### ### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ### ### ##### #### ###### ### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ### ### ##### #### ###### ### #### ######.5</t>
-  </si>
-  <si>
-    <t>#### ### ### ##### ####### ### #### ######.1</t>
-  </si>
-  <si>
-    <t>#### ### ### ##### ####### ### #### ######.2</t>
-  </si>
-  <si>
-    <t>#### ### ### ##### ####### ### #### ######.3</t>
-  </si>
-  <si>
-    <t>#### ### ### ##### ####### ### #### ######.4</t>
-  </si>
-  <si>
-    <t>#### ### ### ##### ####### ### #### ######.5</t>
-  </si>
-  <si>
-    <t>#### ### ### ##### ####### ### #### ######.6</t>
-  </si>
-  <si>
-    <t>#### ### ### ##### ####### ### #### ######.7</t>
-  </si>
-  <si>
-    <t>#### ### ### ##### ####### ### #### ######.8</t>
-  </si>
-  <si>
-    <t>#### ###### ##### #### #### ######.1</t>
-  </si>
-  <si>
-    <t>#### ###### ##### #### #### ######.2</t>
-  </si>
-  <si>
-    <t>#### ###### ##### #### #### ######.3</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### ### #### ######.1</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### ### #### ######.2</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### ### #### ######.3</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### ### #### ######.4</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### ### #### ######.5</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### ### #### ######.6</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### ### #### ######.7</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### ### #### ######.8</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### ### #### ######.9</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### ### #### ######.10</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### ### #### ######.11</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### ### #### ######.12</t>
-  </si>
-  <si>
-    <t>#### ######### ##### #### #### ######.1</t>
-  </si>
-  <si>
-    <t>#### ######### ##### #### #### ######.2</t>
-  </si>
-  <si>
-    <t>#### ######### ##### #### #### ######.3</t>
-  </si>
-  <si>
-    <t>#### ######### ##### #### #### ######.4</t>
-  </si>
-  <si>
-    <t>#### ######### ##### #### #### ######.5</t>
-  </si>
-  <si>
-    <t>####### ##### ####### #### ## #### #### ######.1</t>
-  </si>
-  <si>
-    <t>####### ##### ####### #### ## #### #### ######.2</t>
-  </si>
-  <si>
-    <t>####### ##### ####### #### ## #### #### ######.3</t>
-  </si>
-  <si>
-    <t>####### ##### ####### #### ## #### #### ######.4</t>
-  </si>
-  <si>
-    <t>####### ##### ####### #### ## #### #### ######.5</t>
-  </si>
-  <si>
-    <t>### ######## ####### ####### ####### ### #### ######.1</t>
-  </si>
-  <si>
-    <t>### ######## ####### ####### ####### ### #### ######.2</t>
-  </si>
-  <si>
-    <t>### ######## ####### ####### ####### ### #### ######.3</t>
-  </si>
-  <si>
-    <t>### ######## ####### ####### ####### ### #### ######.4</t>
-  </si>
-  <si>
-    <t>### ######## ####### ####### ####### ### #### ######.5</t>
-  </si>
-  <si>
-    <t>### ######## ####### ####### ####### ### #### ######.6</t>
-  </si>
-  <si>
-    <t>### ######## ####### ####### ####### ### #### ######.7</t>
-  </si>
-  <si>
-    <t>### ######## ####### ####### ####### ### #### ######.8</t>
-  </si>
-  <si>
-    <t>####0 ######## ########### ######### ####### #### ######.1</t>
-  </si>
-  <si>
-    <t>####0 ######## ########### ######### ####### #### ######.2</t>
-  </si>
-  <si>
-    <t>####0 ######## ########### ######### ####### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ####### ######## ####### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ####### ######## ####### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ####### ######## ####### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ####### ######## ####### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ####### ######## ####### #### ######.5</t>
-  </si>
-  <si>
-    <t>###### ####### ######## ####### #### ######.6</t>
-  </si>
-  <si>
-    <t>###### ####### ######## ####### #### ######.7</t>
-  </si>
-  <si>
-    <t>###### ####### ######## ####### #### ######.8</t>
-  </si>
-  <si>
-    <t>###### ####### ######## ####### #### ######.9</t>
-  </si>
-  <si>
-    <t>###### ####### ######## ####### #### ######.10</t>
-  </si>
-  <si>
-    <t>###### ####### ######## ####### #### ######.11</t>
-  </si>
-  <si>
-    <t>##### ######## ####### ##0 ######## ###### ######## ### #### ######.1</t>
-  </si>
-  <si>
-    <t>##### ######## ####### ##0 ######## ###### ######## ### #### ######.2</t>
-  </si>
-  <si>
-    <t>##### ######## ####### ##0 ######## ###### ######## ### #### ######.3</t>
-  </si>
-  <si>
-    <t>##### ######## ####### ##0 ######## ###### ######## ### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### ####### ########### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### ####### ########### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### ####### ########### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### ####### ########### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### ####### ########### #### ######.5</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### ####### ########### #### ######.6</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### ####### ########### #### ######.7</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### ######## ### #### ######.1</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### ######## ### #### ######.2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### ######## ### #### ######.3</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### ######## ### #### ######.4</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### ######## ### #### ######.5</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### ######## ### #### ######.6</t>
-  </si>
-  <si>
-    <t>####### ####### ###### ######## ####### ####### #### ######.1</t>
-  </si>
-  <si>
-    <t>####### ####### ###### ######## ####### ####### #### ######.2</t>
-  </si>
-  <si>
-    <t>####### ####### ###### ######## ####### ####### #### ######.3</t>
-  </si>
-  <si>
-    <t>####### ####### ###### ######## ####### ####### #### ######.4</t>
-  </si>
-  <si>
-    <t>####### ####### ###### ######## ####### ####### #### ######.5</t>
-  </si>
-  <si>
-    <t>####### ####### ###### ######## ####### ####### #### ######.6</t>
-  </si>
-  <si>
-    <t>####### ####### ###### ######## ####### ####### #### ######.7</t>
-  </si>
-  <si>
-    <t>### ### ##### ### ######## ##### ##### #### ######.1</t>
-  </si>
-  <si>
-    <t>### ### ##### ### ######## ##### ##### #### ######.2</t>
-  </si>
-  <si>
-    <t>### ### ##### ### ######## ##### ##### #### ######.3</t>
-  </si>
-  <si>
-    <t>### ### ##### ### ######## ##### ##### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ###### ### ### ######## ##### ##### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ###### ### ### ######## ##### ##### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ###### ### ### ######## ##### ##### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ###### ### ### ######## ##### ##### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ###### ### ### ######## ##### ##### #### ######.5</t>
-  </si>
-  <si>
-    <t>###### ###### ### ### ######## ##### ##### #### ######.6</t>
-  </si>
-  <si>
-    <t>###### ###### ### ### ######## ##### ##### #### ######.7</t>
-  </si>
-  <si>
-    <t>###### ###### ### ### ######## ##### ##### #### ######.8</t>
-  </si>
-  <si>
-    <t>####### #### ##### ##### ####### ### #### ######.1</t>
-  </si>
-  <si>
-    <t>####### #### ##### ##### ####### ### #### ######.2</t>
-  </si>
-  <si>
-    <t>####### #### ##### ##### ####### ### #### ######.3</t>
-  </si>
-  <si>
-    <t>####### #### ##### ##### ####### ### #### ######.4</t>
-  </si>
-  <si>
-    <t>####### #### ##### ##### ####### ### #### ######.5</t>
-  </si>
-  <si>
-    <t>####### #### ##### ##### ####### ### #### ######.8</t>
-  </si>
-  <si>
-    <t>####### #### ##### ##### ####### ### #### ######.7</t>
-  </si>
-  <si>
-    <t>###### #### ######## ###### ##### ####### ####### ### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### #### ######## ###### ##### ####### ####### ### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### #### ######## ###### ##### ####### ####### ### #### ######.3</t>
-  </si>
-  <si>
-    <t>#### ######## ###### ##### ####### ####### ### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### #### ######## ###### ##### ####### ####### ### #### ######.5</t>
-  </si>
-  <si>
-    <t>####### #### ###### ###### ### #### ######.1</t>
-  </si>
-  <si>
-    <t>####### #### ###### ###### ### #### ######.2</t>
-  </si>
-  <si>
-    <t>####### #### ###### ###### ### #### ######.3</t>
-  </si>
-  <si>
-    <t>####### #### ###### ###### ### #### ######.4</t>
-  </si>
-  <si>
-    <t>####### #### ###### ###### ### #### ######.5</t>
-  </si>
-  <si>
-    <t>####### #### ###### ###### ### #### ######.6</t>
-  </si>
-  <si>
-    <t>####### #### ###### ###### ### #### ######.7</t>
-  </si>
-  <si>
-    <t>####### #### ###### ###### ### #### ######.8</t>
-  </si>
-  <si>
-    <t>###### ##### ###### ### ##### ###### ##### ###### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ##### ###### ### ##### ###### ##### ###### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ##### ###### ### ##### ###### ##### ###### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ##### ###### ### ##### ###### ##### ###### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ##### ###### ### ##### ###### ##### ###### #### ######.5</t>
-  </si>
-  <si>
-    <t>###### ##### ####### ######## ##0 #### ###### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ##### ####### ######## ##0 #### ###### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ##### ####### ######## ##0 #### ###### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ##### ####### ######## ##0 #### ###### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ##### ####### ######## ##0 #### ###### #### ######.5</t>
-  </si>
-  <si>
-    <t>###### ##### ####### ######## ##0 #### ###### #### ######.6</t>
-  </si>
-  <si>
-    <t>####### #### ######## ### ##0.## ###### #### ######.1</t>
-  </si>
-  <si>
-    <t>####### #### ######## ### ##0.## ###### #### ######.2</t>
-  </si>
-  <si>
-    <t>####### #### ######## ### ##0.## ###### #### ######.3</t>
-  </si>
-  <si>
-    <t>####### #### ######## ### ##0.## ###### #### ######.4</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ### ####### ###### #### ######.1</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ### ####### ###### #### ######.2</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ### ####### ###### #### ######.3</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ### ####### ###### #### ######.4</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ### ####### ###### #### ######.5</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ### ####### ###### #### ######.6</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ### ####### ###### #### ######.7</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #### ######.1</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #### ######.2</t>
-  </si>
-  <si>
-    <t>####0 ######## ####### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ##### ###### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ##### ###### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ##### ###### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ##### ###### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ######## ######### ####### ###### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ######## ######### ####### ###### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ######## ######### ####### ###### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ######## ######### ####### ###### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ######## ######### ####### ###### #### ######.5</t>
-  </si>
-  <si>
-    <t>###### ######### ###### ### ##### ### ## ###### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ######### ###### ### ##### ### ## ###### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ######### ###### ### ##### ### ## ###### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ######### ###### ### ##### ### ## ###### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ######### ###### ### ##### ### ## ###### #### ######.5</t>
-  </si>
-  <si>
-    <t>###### ######### ###### ### ##### ### ## ###### #### ######.6</t>
-  </si>
-  <si>
-    <t>### ######### ##### ##### ### ## ###### #### ######.1</t>
-  </si>
-  <si>
-    <t>### ######### ##### ##### ### ## ###### #### ######.2</t>
-  </si>
-  <si>
-    <t>### ######### ##### ##### ### ## ###### #### ######.3</t>
-  </si>
-  <si>
-    <t>### ######### ##### ##### ### ## ###### #### ######.4</t>
-  </si>
-  <si>
-    <t>### ######### ##### ##### ### ## ###### #### ######.5</t>
-  </si>
-  <si>
-    <t>######### ######## ###### #### ######.1</t>
-  </si>
-  <si>
-    <t>######### ######## ###### #### ######.2</t>
-  </si>
-  <si>
-    <t>######### ######## ###### #### ######.3</t>
-  </si>
-  <si>
-    <t>######### ######## ###### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ## ###### ## ###### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ## ###### ## ###### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ## ###### ## ###### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ## ###### ## ###### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ## ###### ## ###### #### ######.5</t>
-  </si>
-  <si>
-    <t>######### ####### ###### #### ######.1</t>
-  </si>
-  <si>
-    <t>######### ####### ###### #### ######.2</t>
-  </si>
-  <si>
-    <t>######### ####### ###### #### ######.3</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ##### #### ######.1</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ##### #### ######.2</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ##### #### ######.3</t>
-  </si>
-  <si>
-    <t>####0 ######## ##### ##### #### ######.4</t>
-  </si>
-  <si>
-    <t>##### ######## ######## ##### ##### #### ######.1</t>
-  </si>
-  <si>
-    <t>##### ######## ######## ##### ##### #### ######.2</t>
-  </si>
-  <si>
-    <t>##### ######## ######## ##### ##### #### ######.3</t>
-  </si>
-  <si>
-    <t>######## ##### ######## ######## ####### #### ######.1</t>
-  </si>
-  <si>
-    <t>######## ##### ######## ######## ####### #### ######.2</t>
-  </si>
-  <si>
-    <t>######## ##### ######## ######## ####### #### ######.3</t>
-  </si>
-  <si>
-    <t>######## ##### ######## ######## ####### #### ######.4</t>
-  </si>
-  <si>
-    <t>######## ##### ######## ######## ####### #### ######.5</t>
-  </si>
-  <si>
-    <t>######## ##### ######## ######## ####### #### ######.6</t>
-  </si>
-  <si>
-    <t>######### ######### ###### ###### ###### ##### ######### #### ######.1</t>
-  </si>
-  <si>
-    <t>######### ######### ###### ###### ###### ##### ######### #### ######.2</t>
-  </si>
-  <si>
-    <t>######### ######### ###### ###### ###### ##### ######### #### ######.3</t>
-  </si>
-  <si>
-    <t>######### ######### ###### ###### ###### ##### ######### #### ######.4</t>
-  </si>
-  <si>
-    <t>######### ######### ###### ###### ###### ##### ######### #### ######.5</t>
-  </si>
-  <si>
-    <t>######### ######### ###### ###### ###### ##### ######### #### ######.6</t>
-  </si>
-  <si>
-    <t>### ###### #0 ###### ##### ##### #### ### #### ######.1</t>
-  </si>
-  <si>
-    <t>### ###### #0 ###### ##### ##### #### ### #### ######.2</t>
-  </si>
-  <si>
-    <t>### ###### #0 ###### ##### ##### #### ### #### ######.3</t>
-  </si>
-  <si>
-    <t>### ###### #0 ###### ##### ##### #### ### #### ######.4</t>
-  </si>
-  <si>
-    <t>### ###### #0 ###### ##### ##### #### ### #### ######.5</t>
-  </si>
-  <si>
-    <t>### ###### #0 ###### ##### ##### #### ### #### ######.6</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##0.## ############ ###### ####### ### #### #### ######.1</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##0.## ############ ###### ####### ### #### #### ######.2</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##0.## ############ ###### ####### ### #### #### ######.3</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##0.## ############ ###### ####### ### #### #### ######.4</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##0.## ############ ###### ####### ### #### #### ######.5</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##0.## ############ ###### ####### ### #### #### ######.6</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##0.## ############ ###### ####### ### #### #### ######.7</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##0.## ############ ###### ####### ### #### #### ######.8</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##0.## ############ ###### ####### ### #### #### ######.9</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##0.## ############ ###### ####### ### #### #### ######.10</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##0.## ############ ###### ####### ### #### #### ######.11</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##0.## ############ ###### ####### ### #### #### ######.12</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##0.## ############ ###### ####### ### #### #### ######.13</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #### ######.1</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #### ######.2</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #### ######.3</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #### ######.4</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #### ######.5</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #### ######.6</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #### ######.7</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #### ######.8</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #### ######.9</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #### ######.10</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #### ######.11</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #### ######.12</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ####### #### ######.13</t>
-  </si>
-  <si>
-    <t>##### ######## ######## ####### ##### #### ######.1</t>
-  </si>
-  <si>
-    <t>##### ######## ######## ####### ##### #### ######.2</t>
-  </si>
-  <si>
-    <t>## ## ######## ##### ###### #### ######.1</t>
-  </si>
-  <si>
-    <t>## ## ######## ##### ###### #### ######.2</t>
-  </si>
-  <si>
-    <t>## ## ######## ##### ###### #### ######.3</t>
-  </si>
-  <si>
-    <t>## ## ######## ##### ###### #### ######.4</t>
-  </si>
-  <si>
-    <t>## ## ######## ##### ###### #### ######.5</t>
-  </si>
-  <si>
-    <t>###### ###### ###### ###### ## ### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ###### ###### ###### ## ### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ###### ###### ###### ## ### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ###### ###### ###### ## ### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ###### ###### ###### ## ### #### ######.5</t>
-  </si>
-  <si>
-    <t>###### ###### ###### ###### ## ### #### ######.6</t>
-  </si>
-  <si>
-    <t>###### ###### ###### ###### ## ### #### ######.7</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### ######.1</t>
-  </si>
-  <si>
-    <t>####0 ######## #### #### ######.2</t>
-  </si>
-  <si>
-    <t>######## ### ##0 ####### ####### ### #### ######.1</t>
-  </si>
-  <si>
-    <t>######## ### ##0 ####### ####### ### #### ######.2</t>
-  </si>
-  <si>
-    <t>######## ### ##0 ####### ####### ### #### ######.3</t>
-  </si>
-  <si>
-    <t>######## ### ##0 ####### ####### ### #### ######.4</t>
-  </si>
-  <si>
-    <t>######## ### ##0 ####### ####### ### #### ######.5</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.1</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.2</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.3</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.4</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.5</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.6</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.7</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.8</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.9</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.10</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.11</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.12</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.13</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.14</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.15</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.16</t>
-  </si>
-  <si>
-    <t>### ## ### ####### ### #### ######.17</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ##0.# #### ## ############# #### ######.1</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ##0.# #### ## ############# #### ######.2</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ##0.# #### ## ############# #### ######.3</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ##0.# #### ## ############# #### ######.4</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ##0.# #### ## ############# #### ######.5</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ##0.# #### ## ############# #### ######.6</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ##0.# #### ## ############# #### ######.7</t>
-  </si>
-  <si>
-    <t>### ###### ##### ##### ##0.# #### ## ############# #### ######.8</t>
-  </si>
-  <si>
-    <t>### ##### ##### ##### ########## 60 #### ### #### ######.1</t>
-  </si>
-  <si>
-    <t>### ##### ##### ##### ########## 60 #### ### #### ######.2</t>
-  </si>
-  <si>
-    <t>### ##### ##### ##### ########## 60 #### ### #### ######.3</t>
-  </si>
-  <si>
-    <t>### ##### ##### ##### ########## 60 #### ### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ######### ##### ###### ###### ##### #### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ######### ##### ###### ###### ##### #### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ######### ##### ###### ###### ##### #### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ######### ##### ###### ###### ##### #### #### ######.4</t>
-  </si>
-  <si>
-    <t>####### ##### ######### #### ######.1</t>
-  </si>
-  <si>
-    <t>####### ##### ######### #### ######.2</t>
-  </si>
-  <si>
-    <t>####### ##### ######### #### ######.3</t>
-  </si>
-  <si>
-    <t>####### ##### ######### #### ######.4</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##### ##### ##### #### #### ######.1</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##### ##### ##### #### #### ######.2</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##### ##### ##### #### #### ######.3</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##### ##### ##### #### #### ######.4</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##### ##### ##### #### #### ######.5</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##### ##### ##### #### #### ######.6</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##### ##### ##### #### #### ######.7</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##### ##### ##### #### #### ######.8</t>
-  </si>
-  <si>
-    <t>### #### ###### ##### ####### #### ######.1</t>
-  </si>
-  <si>
-    <t>### #### ###### ##### ####### #### ######.2</t>
-  </si>
-  <si>
-    <t>### #### ###### ##### ####### #### ######.3</t>
-  </si>
-  <si>
-    <t>### #### ###### ##### ####### #### ######.4</t>
-  </si>
-  <si>
-    <t>### #### ###### ##### ####### #### ######.5</t>
-  </si>
-  <si>
-    <t>### #### ###### ##### ####### #### ######.6</t>
-  </si>
-  <si>
-    <t>### #### ###### ##### ####### #### ######.7</t>
-  </si>
-  <si>
-    <t>##### ######## ##### ##### ##0 # ######### #### ######.1</t>
-  </si>
-  <si>
-    <t>##### ######## ##### ##### ##0 # ######### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ## ##### ##0 ## ##### #### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ## ##### ##0 ## ##### #### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ## ##### ##0 ## ##### #### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ## ##### ##0 ## ##### #### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ## ##### ##0 ## ##### #### #### ######.5</t>
-  </si>
-  <si>
-    <t>###### ## ##### ##0 ## ##### #### #### ######.6</t>
-  </si>
-  <si>
-    <t>###### ## ##### ##0 ## ##### #### #### ######.7</t>
-  </si>
-  <si>
-    <t>###### ## ##### ##0 ## ##### #### #### ######.8</t>
-  </si>
-  <si>
-    <t>###### ## ##### ##0 ## ##### #### #### ######.9</t>
-  </si>
-  <si>
-    <t>###### ## ##### ##0 ## ##### #### #### ######.10</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ##### ##### ######### #### ######.1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ##### ##### ######### #### ######.2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ##### ##### ######### #### ######.3</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ##### ##### ######### #### ######.4</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ##### ##### ######### #### ######.5</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ##### ##### ######### #### ######.6</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ##### ##### ######### #### ######.7</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ##### ##### ######### #### ######.8</t>
-  </si>
-  <si>
-    <t>#### #### #### ##### ######### #### ######.1</t>
-  </si>
-  <si>
-    <t>#### #### #### ##### ######### #### ######.2</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ##### #### ######.1</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ##### #### ######.2</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ##### #### ######.3</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ##### #### ######.4</t>
-  </si>
-  <si>
-    <t>####0 ######## #### ##### #### ######.5</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ###### ### #### ######.1</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ###### ### #### ######.2</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ###### ### #### ######.3</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ###### ### #### ######.4</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ###### ### #### ######.5</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ###### ### #### ######.6</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -1352,8 +404,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1369,7 +429,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1377,12 +437,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1681,91 +759,169 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>420</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>421</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>422</v>
+        <v>106</v>
       </c>
       <c r="F2" t="s">
-        <v>423</v>
+        <v>107</v>
       </c>
       <c r="G2" t="s">
-        <v>424</v>
+        <v>108</v>
       </c>
       <c r="H2" t="s">
-        <v>425</v>
+        <v>109</v>
       </c>
       <c r="I2" t="s">
-        <v>426</v>
+        <v>110</v>
       </c>
       <c r="J2" t="s">
-        <v>427</v>
+        <v>111</v>
       </c>
       <c r="K2" t="s">
-        <v>428</v>
+        <v>112</v>
       </c>
       <c r="L2" t="s">
-        <v>429</v>
+        <v>113</v>
       </c>
       <c r="M2" t="s">
-        <v>430</v>
+        <v>114</v>
       </c>
       <c r="N2" t="s">
-        <v>431</v>
+        <v>115</v>
       </c>
       <c r="O2" t="s">
-        <v>432</v>
+        <v>116</v>
       </c>
       <c r="P2" t="s">
-        <v>433</v>
+        <v>117</v>
       </c>
       <c r="Q2" t="s">
-        <v>434</v>
+        <v>118</v>
       </c>
       <c r="R2" t="s">
-        <v>435</v>
+        <v>119</v>
       </c>
       <c r="S2" t="s">
-        <v>436</v>
+        <v>120</v>
       </c>
       <c r="T2" t="s">
-        <v>437</v>
+        <v>121</v>
       </c>
       <c r="U2" t="s">
-        <v>438</v>
+        <v>122</v>
       </c>
       <c r="V2" t="s">
-        <v>439</v>
+        <v>123</v>
       </c>
       <c r="W2" t="s">
-        <v>440</v>
+        <v>124</v>
       </c>
       <c r="X2" t="s">
-        <v>441</v>
+        <v>125</v>
       </c>
       <c r="Y2" t="s">
-        <v>441</v>
+        <v>125</v>
       </c>
       <c r="Z2" t="s">
-        <v>442</v>
+        <v>126</v>
       </c>
       <c r="AA2" t="s">
-        <v>443</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -1773,7 +929,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>1172</v>
@@ -1856,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>1109</v>
@@ -1939,7 +1095,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>1175</v>
@@ -2022,7 +1178,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>1173</v>
@@ -2105,7 +1261,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>1026</v>
@@ -2188,7 +1344,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>1152</v>
@@ -2271,7 +1427,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>1198</v>
@@ -2354,7 +1510,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C10">
         <v>1104</v>
@@ -2437,7 +1593,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C11">
         <v>1211</v>
@@ -2520,7 +1676,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C12">
         <v>720</v>
@@ -2603,7 +1759,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C13">
         <v>1181</v>
@@ -2686,7 +1842,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>1163</v>
@@ -2769,7 +1925,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C15">
         <v>885</v>
@@ -2852,7 +2008,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C16">
         <v>1049</v>
@@ -2935,7 +2091,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C17">
         <v>1185</v>
@@ -3018,7 +2174,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C18">
         <v>1124</v>
@@ -3101,7 +2257,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C19">
         <v>1183</v>
@@ -3184,7 +2340,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C20">
         <v>1183</v>
@@ -3267,7 +2423,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>1165</v>
@@ -3350,7 +2506,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C22">
         <v>1040</v>
@@ -3433,7 +2589,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C23">
         <v>1183</v>
@@ -3516,7 +2672,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C24">
         <v>727</v>
@@ -3599,7 +2755,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C25">
         <v>1163</v>
@@ -3682,7 +2838,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C26">
         <v>1147</v>
@@ -3765,7 +2921,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>1138</v>
@@ -3848,7 +3004,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C28">
         <v>1163</v>
@@ -4014,7 +3170,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30">
         <v>891</v>
@@ -4097,7 +3253,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C31">
         <v>1162</v>
@@ -4180,7 +3336,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C32">
         <v>1183</v>
@@ -4263,7 +3419,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C33">
         <v>1133</v>
@@ -4346,7 +3502,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C34">
         <v>1143</v>
@@ -4429,7 +3585,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C35">
         <v>977</v>
@@ -4512,7 +3668,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C36">
         <v>1162</v>
@@ -4595,7 +3751,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C37">
         <v>1157</v>
@@ -4678,7 +3834,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C38">
         <v>1158</v>
@@ -4761,7 +3917,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C39">
         <v>1107</v>
@@ -4844,7 +4000,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C40">
         <v>656</v>
@@ -4927,7 +4083,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C41">
         <v>1185</v>
@@ -5010,7 +4166,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C42">
         <v>1159</v>
@@ -5093,7 +4249,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C43">
         <v>1199</v>
@@ -5176,7 +4332,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C44">
         <v>1234</v>
@@ -5259,7 +4415,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C45">
         <v>1165</v>
@@ -5342,7 +4498,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C46">
         <v>659</v>
@@ -5425,7 +4581,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C47">
         <v>1109</v>
@@ -5508,7 +4664,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C48">
         <v>1038</v>
@@ -5591,7 +4747,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C49">
         <v>679</v>
@@ -5674,7 +4830,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C50">
         <v>1021</v>
@@ -5757,7 +4913,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C51">
         <v>1157</v>
@@ -5840,7 +4996,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C52">
         <v>1128</v>
@@ -5923,7 +5079,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C53">
         <v>1017</v>
@@ -6006,7 +5162,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C54">
         <v>975</v>
@@ -6089,7 +5245,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C55">
         <v>1051</v>
@@ -6172,7 +5328,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C56">
         <v>1188</v>
@@ -6255,7 +5411,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="C57">
         <v>907</v>
@@ -6338,7 +5494,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C58">
         <v>1171</v>
@@ -6421,7 +5577,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C59">
         <v>1234</v>
@@ -6504,7 +5660,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C60">
         <v>1178</v>
@@ -6587,7 +5743,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C61">
         <v>1166</v>
@@ -6670,7 +5826,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="C62">
         <v>1048</v>
@@ -6753,7 +5909,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="C63">
         <v>1097</v>
@@ -6836,7 +5992,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C64">
         <v>1134</v>
@@ -6919,7 +6075,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="C65">
         <v>1178</v>
@@ -7002,7 +6158,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="C66">
         <v>1152</v>
@@ -7085,7 +6241,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C67">
         <v>1026</v>
@@ -7168,7 +6324,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C68">
         <v>1048</v>
@@ -7251,7 +6407,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="C69">
         <v>694</v>
@@ -7334,7 +6490,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="C70">
         <v>1167</v>
@@ -7417,7 +6573,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="C71">
         <v>1063</v>
@@ -7500,7 +6656,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="C72">
         <v>1189</v>
@@ -7583,7 +6739,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="C73">
         <v>1146</v>
@@ -7666,7 +6822,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="C74">
         <v>943</v>
@@ -7749,7 +6905,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="C75">
         <v>934</v>
@@ -7832,7 +6988,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="C76">
         <v>724</v>
@@ -7915,7 +7071,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="C77">
         <v>1079</v>
@@ -7998,7 +7154,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C78">
         <v>1160</v>
@@ -8081,7 +7237,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C79">
         <v>750</v>
@@ -8164,7 +7320,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="C80">
         <v>719</v>
@@ -8247,7 +7403,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="C81">
         <v>669</v>
@@ -8330,7 +7486,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="C82">
         <v>1213</v>
@@ -8413,7 +7569,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="C83">
         <v>1119</v>
@@ -8496,7 +7652,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="C84">
         <v>1165</v>
@@ -8579,7 +7735,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C85">
         <v>1226</v>
@@ -8662,7 +7818,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="C86">
         <v>1115</v>
@@ -8745,7 +7901,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="C87">
         <v>1106</v>
@@ -8828,7 +7984,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="C88">
         <v>1193</v>
@@ -8911,7 +8067,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="C89">
         <v>1145</v>
@@ -8994,7 +8150,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="C90">
         <v>1002</v>
@@ -9077,7 +8233,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="C91">
         <v>901</v>
@@ -9160,7 +8316,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="C92">
         <v>940</v>
@@ -9243,7 +8399,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="C93">
         <v>676</v>
@@ -9326,7 +8482,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="C94">
         <v>1093</v>
@@ -9409,7 +8565,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="C95">
         <v>778</v>
@@ -9492,7 +8648,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="C96">
         <v>652</v>
@@ -9575,7 +8731,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="C97">
         <v>1135</v>
@@ -9658,7 +8814,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="C98">
         <v>709</v>
@@ -9741,7 +8897,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="C99">
         <v>1116</v>
@@ -9824,7 +8980,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="C100">
         <v>1166</v>
@@ -9907,7 +9063,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="C101">
         <v>1207</v>
@@ -9990,7 +9146,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="C102">
         <v>1167</v>
@@ -10073,7 +9229,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="C103">
         <v>1024</v>
@@ -10156,7 +9312,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="C104">
         <v>789</v>
@@ -10239,7 +9395,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="C105">
         <v>1208</v>
@@ -10322,7 +9478,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="C106">
         <v>856</v>
@@ -10405,7 +9561,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
       <c r="C107">
         <v>1142</v>
@@ -10488,7 +9644,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C108">
         <v>1056</v>
@@ -10571,7 +9727,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="C109">
         <v>1173</v>
@@ -10654,7 +9810,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="C110">
         <v>1067</v>
@@ -10737,7 +9893,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="C111">
         <v>1057</v>
@@ -10820,7 +9976,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="C112">
         <v>1030</v>
@@ -10903,7 +10059,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="C113">
         <v>1085</v>
@@ -10986,7 +10142,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>29</v>
       </c>
       <c r="C114">
         <v>1021</v>
@@ -11069,7 +10225,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="C115">
         <v>943</v>
@@ -11152,7 +10308,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="C116">
         <v>859</v>
@@ -11235,7 +10391,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="C117">
         <v>1116</v>
@@ -11318,7 +10474,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="C118">
         <v>1202</v>
@@ -11401,7 +10557,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="C119">
         <v>1147</v>
@@ -11484,7 +10640,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="C120">
         <v>1100</v>
@@ -11567,7 +10723,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>29</v>
       </c>
       <c r="C121">
         <v>1228</v>
@@ -11650,7 +10806,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="C122">
         <v>1194</v>
@@ -11733,7 +10889,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="C123">
         <v>1133</v>
@@ -11816,7 +10972,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="C124">
         <v>1151</v>
@@ -11899,7 +11055,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="C125">
         <v>1115</v>
@@ -11982,7 +11138,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="C126">
         <v>1125</v>
@@ -12065,7 +11221,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="C127">
         <v>1104</v>
@@ -12148,7 +11304,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="C128">
         <v>1242</v>
@@ -12231,7 +11387,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="C129">
         <v>1143</v>
@@ -12314,7 +11470,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="C130">
         <v>1131</v>
@@ -12397,7 +11553,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="C131">
         <v>1132</v>
@@ -12480,7 +11636,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="C132">
         <v>1144</v>
@@ -12563,7 +11719,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>29</v>
       </c>
       <c r="C133">
         <v>1116</v>
@@ -12646,7 +11802,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>29</v>
       </c>
       <c r="C134">
         <v>1128</v>
@@ -12729,7 +11885,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="C135">
         <v>1093</v>
@@ -12812,7 +11968,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="C136">
         <v>997</v>
@@ -12895,7 +12051,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>29</v>
       </c>
       <c r="C137">
         <v>821</v>
@@ -12978,7 +12134,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
       <c r="C138">
         <v>1128</v>
@@ -13061,7 +12217,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>29</v>
       </c>
       <c r="C139">
         <v>1066</v>
@@ -13144,7 +12300,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="C140">
         <v>1145</v>
@@ -13227,7 +12383,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="C141">
         <v>1179</v>
@@ -13310,7 +12466,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="C142">
         <v>1205</v>
@@ -13393,7 +12549,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="C143">
         <v>1154</v>
@@ -13476,7 +12632,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="C144">
         <v>1186</v>
@@ -13559,7 +12715,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>29</v>
       </c>
       <c r="C145">
         <v>1228</v>
@@ -13642,7 +12798,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="C146">
         <v>1157</v>
@@ -13725,7 +12881,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>29</v>
       </c>
       <c r="C147">
         <v>1153</v>
@@ -13808,7 +12964,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>29</v>
       </c>
       <c r="C148">
         <v>1222</v>
@@ -13891,7 +13047,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="C149">
         <v>1162</v>
@@ -13974,7 +13130,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="C150">
         <v>1096</v>
@@ -14057,7 +13213,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>29</v>
       </c>
       <c r="C151">
         <v>798</v>
@@ -14140,7 +13296,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>29</v>
       </c>
       <c r="C152">
         <v>1058</v>
@@ -14223,7 +13379,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>29</v>
       </c>
       <c r="C153">
         <v>1012</v>
@@ -14306,7 +13462,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>29</v>
       </c>
       <c r="C154">
         <v>1183</v>
@@ -14389,7 +13545,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c r="C155">
         <v>1005</v>
@@ -14472,7 +13628,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>29</v>
       </c>
       <c r="C156">
         <v>1008</v>
@@ -14555,7 +13711,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>29</v>
       </c>
       <c r="C157">
         <v>1177</v>
@@ -14638,7 +13794,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="C158">
         <v>1176</v>
@@ -14721,7 +13877,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>29</v>
       </c>
       <c r="C159">
         <v>1218</v>
@@ -14804,7 +13960,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>29</v>
       </c>
       <c r="C160">
         <v>1127</v>
@@ -14887,7 +14043,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>29</v>
       </c>
       <c r="C161">
         <v>1159</v>
@@ -14970,7 +14126,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>29</v>
       </c>
       <c r="C162">
         <v>664</v>
@@ -15053,7 +14209,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>29</v>
       </c>
       <c r="C163">
         <v>1178</v>
@@ -15136,7 +14292,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>29</v>
       </c>
       <c r="C164">
         <v>1070</v>
@@ -15219,7 +14375,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="C165">
         <v>1162</v>
@@ -15302,7 +14458,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>29</v>
       </c>
       <c r="C166">
         <v>1220</v>
@@ -15385,7 +14541,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>29</v>
       </c>
       <c r="C167">
         <v>1187</v>
@@ -15468,7 +14624,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>29</v>
       </c>
       <c r="C168">
         <v>1157</v>
@@ -15551,7 +14707,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>29</v>
       </c>
       <c r="C169">
         <v>659</v>
@@ -15634,7 +14790,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>29</v>
       </c>
       <c r="C170">
         <v>1206</v>
@@ -15717,7 +14873,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>29</v>
       </c>
       <c r="C171">
         <v>1160</v>
@@ -15800,7 +14956,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>29</v>
       </c>
       <c r="C172">
         <v>1130</v>
@@ -15883,7 +15039,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>29</v>
       </c>
       <c r="C173">
         <v>1144</v>
@@ -15966,7 +15122,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>30</v>
       </c>
       <c r="C174">
         <v>1155</v>
@@ -16049,7 +15205,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="C175">
         <v>1085</v>
@@ -16132,7 +15288,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>29</v>
       </c>
       <c r="C176">
         <v>1046</v>
@@ -16215,7 +15371,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>29</v>
       </c>
       <c r="C177">
         <v>1035</v>
@@ -16298,7 +15454,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>29</v>
       </c>
       <c r="C178">
         <v>1157</v>
@@ -16381,7 +15537,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>29</v>
       </c>
       <c r="C179">
         <v>1149</v>
@@ -16464,7 +15620,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>29</v>
       </c>
       <c r="C180">
         <v>943</v>
@@ -16547,7 +15703,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>29</v>
       </c>
       <c r="C181">
         <v>1039</v>
@@ -16630,7 +15786,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>29</v>
       </c>
       <c r="C182">
         <v>1117</v>
@@ -16713,7 +15869,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>29</v>
       </c>
       <c r="C183">
         <v>1035</v>
@@ -16796,7 +15952,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>29</v>
       </c>
       <c r="C184">
         <v>1050</v>
@@ -16879,7 +16035,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>29</v>
       </c>
       <c r="C185">
         <v>550</v>
@@ -16962,7 +16118,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>29</v>
       </c>
       <c r="C186">
         <v>906</v>
@@ -17045,7 +16201,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>29</v>
       </c>
       <c r="C187">
         <v>1045</v>
@@ -17128,7 +16284,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>29</v>
       </c>
       <c r="C188">
         <v>1014</v>
@@ -17211,7 +16367,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="C189">
         <v>1060</v>
@@ -17294,7 +16450,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>29</v>
       </c>
       <c r="C190">
         <v>1142</v>
@@ -17377,7 +16533,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="C191">
         <v>1149</v>
@@ -17460,7 +16616,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>29</v>
       </c>
       <c r="C192">
         <v>1154</v>
@@ -17543,7 +16699,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="C193">
         <v>1111</v>
@@ -17626,7 +16782,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="C194">
         <v>925</v>
@@ -17709,7 +16865,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>194</v>
+        <v>29</v>
       </c>
       <c r="C195">
         <v>809</v>
@@ -17792,7 +16948,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>195</v>
+        <v>29</v>
       </c>
       <c r="C196">
         <v>1086</v>
@@ -17875,7 +17031,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>196</v>
+        <v>29</v>
       </c>
       <c r="C197">
         <v>1159</v>
@@ -17958,7 +17114,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>197</v>
+        <v>29</v>
       </c>
       <c r="C198">
         <v>762</v>
@@ -18041,7 +17197,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>198</v>
+        <v>29</v>
       </c>
       <c r="C199">
         <v>1228</v>
@@ -18124,7 +17280,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>199</v>
+        <v>29</v>
       </c>
       <c r="C200">
         <v>747</v>
@@ -18207,7 +17363,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>200</v>
+        <v>29</v>
       </c>
       <c r="C201">
         <v>1117</v>
@@ -18290,7 +17446,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>201</v>
+        <v>29</v>
       </c>
       <c r="C202">
         <v>1124</v>
@@ -18373,7 +17529,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>202</v>
+        <v>29</v>
       </c>
       <c r="C203">
         <v>756</v>
@@ -18456,7 +17612,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>203</v>
+        <v>29</v>
       </c>
       <c r="C204">
         <v>799</v>
@@ -18539,7 +17695,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>204</v>
+        <v>29</v>
       </c>
       <c r="C205">
         <v>1057</v>
@@ -18622,7 +17778,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>205</v>
+        <v>29</v>
       </c>
       <c r="C206">
         <v>802</v>
@@ -18705,7 +17861,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>206</v>
+        <v>29</v>
       </c>
       <c r="C207">
         <v>1234</v>
@@ -18788,7 +17944,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>207</v>
+        <v>29</v>
       </c>
       <c r="C208">
         <v>1113</v>
@@ -18871,7 +18027,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>208</v>
+        <v>29</v>
       </c>
       <c r="C209">
         <v>1225</v>
@@ -18954,7 +18110,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>209</v>
+        <v>29</v>
       </c>
       <c r="C210">
         <v>879</v>
@@ -19037,7 +18193,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>210</v>
+        <v>29</v>
       </c>
       <c r="C211">
         <v>888</v>
@@ -19120,7 +18276,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>211</v>
+        <v>29</v>
       </c>
       <c r="C212">
         <v>1088</v>
@@ -19203,7 +18359,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>212</v>
+        <v>29</v>
       </c>
       <c r="C213">
         <v>1072</v>
@@ -19286,7 +18442,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>213</v>
+        <v>29</v>
       </c>
       <c r="C214">
         <v>948</v>
@@ -19369,7 +18525,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>214</v>
+        <v>29</v>
       </c>
       <c r="C215">
         <v>1024</v>
@@ -19452,7 +18608,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>215</v>
+        <v>29</v>
       </c>
       <c r="C216">
         <v>1170</v>
@@ -19535,7 +18691,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>216</v>
+        <v>29</v>
       </c>
       <c r="C217">
         <v>1184</v>
@@ -19618,7 +18774,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>217</v>
+        <v>29</v>
       </c>
       <c r="C218">
         <v>989</v>
@@ -19701,7 +18857,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>218</v>
+        <v>29</v>
       </c>
       <c r="C219">
         <v>993</v>
@@ -19784,7 +18940,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>219</v>
+        <v>29</v>
       </c>
       <c r="C220">
         <v>1015</v>
@@ -19867,7 +19023,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>220</v>
+        <v>29</v>
       </c>
       <c r="C221">
         <v>736</v>
@@ -19950,7 +19106,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>221</v>
+        <v>29</v>
       </c>
       <c r="C222">
         <v>1152</v>
@@ -20033,7 +19189,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>222</v>
+        <v>29</v>
       </c>
       <c r="C223">
         <v>1131</v>
@@ -20116,7 +19272,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>223</v>
+        <v>29</v>
       </c>
       <c r="C224">
         <v>1110</v>
@@ -20199,7 +19355,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>224</v>
+        <v>29</v>
       </c>
       <c r="C225">
         <v>1147</v>
@@ -20282,7 +19438,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>225</v>
+        <v>29</v>
       </c>
       <c r="C226">
         <v>1180</v>
@@ -20365,7 +19521,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>226</v>
+        <v>29</v>
       </c>
       <c r="C227">
         <v>1135</v>
@@ -20448,7 +19604,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>227</v>
+        <v>29</v>
       </c>
       <c r="C228">
         <v>1161</v>
@@ -20531,7 +19687,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>228</v>
+        <v>29</v>
       </c>
       <c r="C229">
         <v>820</v>
@@ -20614,7 +19770,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>229</v>
+        <v>29</v>
       </c>
       <c r="C230">
         <v>1067</v>
@@ -20697,7 +19853,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>230</v>
+        <v>29</v>
       </c>
       <c r="C231">
         <v>745</v>
@@ -20780,7 +19936,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>231</v>
+        <v>29</v>
       </c>
       <c r="C232">
         <v>1094</v>
@@ -20863,7 +20019,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>232</v>
+        <v>29</v>
       </c>
       <c r="C233">
         <v>1043</v>
@@ -20946,7 +20102,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>233</v>
+        <v>29</v>
       </c>
       <c r="C234">
         <v>1160</v>
@@ -21029,7 +20185,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="C235">
         <v>1137</v>
@@ -21112,7 +20268,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>235</v>
+        <v>29</v>
       </c>
       <c r="C236">
         <v>1188</v>
@@ -21195,7 +20351,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>236</v>
+        <v>29</v>
       </c>
       <c r="C237">
         <v>909</v>
@@ -21278,7 +20434,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>237</v>
+        <v>29</v>
       </c>
       <c r="C238">
         <v>947</v>
@@ -21361,7 +20517,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>238</v>
+        <v>29</v>
       </c>
       <c r="C239">
         <v>1226</v>
@@ -21444,7 +20600,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="C240">
         <v>1220</v>
@@ -21527,7 +20683,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>240</v>
+        <v>29</v>
       </c>
       <c r="C241">
         <v>1135</v>
@@ -21610,7 +20766,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>241</v>
+        <v>29</v>
       </c>
       <c r="C242">
         <v>1204</v>
@@ -21693,7 +20849,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="C243">
         <v>1164</v>
@@ -21776,7 +20932,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>243</v>
+        <v>29</v>
       </c>
       <c r="C244">
         <v>786</v>
@@ -21859,7 +21015,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>244</v>
+        <v>29</v>
       </c>
       <c r="C245">
         <v>933</v>
@@ -21942,7 +21098,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>245</v>
+        <v>29</v>
       </c>
       <c r="C246">
         <v>1013</v>
@@ -22025,7 +21181,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>246</v>
+        <v>29</v>
       </c>
       <c r="C247">
         <v>1146</v>
@@ -22108,7 +21264,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>247</v>
+        <v>29</v>
       </c>
       <c r="C248">
         <v>1056</v>
@@ -22191,7 +21347,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>248</v>
+        <v>29</v>
       </c>
       <c r="C249">
         <v>984</v>
@@ -22274,7 +21430,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>249</v>
+        <v>29</v>
       </c>
       <c r="C250">
         <v>1071</v>
@@ -22357,7 +21513,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>250</v>
+        <v>29</v>
       </c>
       <c r="C251">
         <v>850</v>
@@ -22440,7 +21596,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>251</v>
+        <v>29</v>
       </c>
       <c r="C252">
         <v>1155</v>
@@ -22523,7 +21679,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>252</v>
+        <v>29</v>
       </c>
       <c r="C253">
         <v>1205</v>
@@ -22606,7 +21762,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>253</v>
+        <v>29</v>
       </c>
       <c r="C254">
         <v>938</v>
@@ -22689,7 +21845,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>254</v>
+        <v>29</v>
       </c>
       <c r="C255">
         <v>1002</v>
@@ -22772,7 +21928,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>255</v>
+        <v>29</v>
       </c>
       <c r="C256">
         <v>938</v>
@@ -22855,7 +22011,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>256</v>
+        <v>29</v>
       </c>
       <c r="C257">
         <v>811</v>
@@ -22938,7 +22094,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>257</v>
+        <v>29</v>
       </c>
       <c r="C258">
         <v>950</v>
@@ -23021,7 +22177,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>258</v>
+        <v>29</v>
       </c>
       <c r="C259">
         <v>808</v>
@@ -23104,7 +22260,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>259</v>
+        <v>29</v>
       </c>
       <c r="C260">
         <v>1123</v>
@@ -23187,7 +22343,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>260</v>
+        <v>29</v>
       </c>
       <c r="C261">
         <v>877</v>
@@ -23270,7 +22426,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="C262">
         <v>725</v>
@@ -23353,7 +22509,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>262</v>
+        <v>29</v>
       </c>
       <c r="C263">
         <v>710</v>
@@ -23436,7 +22592,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>263</v>
+        <v>29</v>
       </c>
       <c r="C264">
         <v>1173</v>
@@ -23519,7 +22675,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>264</v>
+        <v>29</v>
       </c>
       <c r="C265">
         <v>813</v>
@@ -23602,7 +22758,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>265</v>
+        <v>29</v>
       </c>
       <c r="C266">
         <v>1146</v>
@@ -23685,7 +22841,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>266</v>
+        <v>29</v>
       </c>
       <c r="C267">
         <v>1153</v>
@@ -23768,7 +22924,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>267</v>
+        <v>29</v>
       </c>
       <c r="C268">
         <v>1226</v>
@@ -23851,7 +23007,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>268</v>
+        <v>29</v>
       </c>
       <c r="C269">
         <v>1164</v>
@@ -23934,7 +23090,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>269</v>
+        <v>29</v>
       </c>
       <c r="C270">
         <v>1218</v>
@@ -24017,7 +23173,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>270</v>
+        <v>29</v>
       </c>
       <c r="C271">
         <v>1196</v>
@@ -24100,7 +23256,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c r="C272">
         <v>1173</v>
@@ -24183,7 +23339,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>272</v>
+        <v>29</v>
       </c>
       <c r="C273">
         <v>1099</v>
@@ -24266,7 +23422,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>273</v>
+        <v>29</v>
       </c>
       <c r="C274">
         <v>1111</v>
@@ -24349,7 +23505,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>274</v>
+        <v>29</v>
       </c>
       <c r="C275">
         <v>1122</v>
@@ -24432,7 +23588,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>275</v>
+        <v>29</v>
       </c>
       <c r="C276">
         <v>1151</v>
@@ -24515,7 +23671,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>276</v>
+        <v>29</v>
       </c>
       <c r="C277">
         <v>646</v>
@@ -24598,7 +23754,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>277</v>
+        <v>29</v>
       </c>
       <c r="C278">
         <v>1245</v>
@@ -24681,7 +23837,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>278</v>
+        <v>29</v>
       </c>
       <c r="C279">
         <v>1197</v>
@@ -24764,7 +23920,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>279</v>
+        <v>29</v>
       </c>
       <c r="C280">
         <v>1136</v>
@@ -24847,7 +24003,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>280</v>
+        <v>29</v>
       </c>
       <c r="C281">
         <v>1111</v>
@@ -24930,7 +24086,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>281</v>
+        <v>29</v>
       </c>
       <c r="C282">
         <v>666</v>
@@ -25013,7 +24169,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>282</v>
+        <v>29</v>
       </c>
       <c r="C283">
         <v>655</v>
@@ -25096,7 +24252,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>283</v>
+        <v>29</v>
       </c>
       <c r="C284">
         <v>1217</v>
@@ -25179,7 +24335,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>284</v>
+        <v>29</v>
       </c>
       <c r="C285">
         <v>1183</v>
@@ -25262,7 +24418,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>285</v>
+        <v>29</v>
       </c>
       <c r="C286">
         <v>1174</v>
@@ -25345,7 +24501,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>286</v>
+        <v>29</v>
       </c>
       <c r="C287">
         <v>718</v>
@@ -25428,7 +24584,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>287</v>
+        <v>29</v>
       </c>
       <c r="C288">
         <v>1155</v>
@@ -25511,7 +24667,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>288</v>
+        <v>29</v>
       </c>
       <c r="C289">
         <v>718</v>
@@ -25594,7 +24750,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>289</v>
+        <v>29</v>
       </c>
       <c r="C290">
         <v>1232</v>
@@ -25677,7 +24833,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>290</v>
+        <v>29</v>
       </c>
       <c r="C291">
         <v>1227</v>
@@ -25760,7 +24916,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>291</v>
+        <v>29</v>
       </c>
       <c r="C292">
         <v>1136</v>
@@ -25843,7 +24999,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>292</v>
+        <v>29</v>
       </c>
       <c r="C293">
         <v>1136</v>
@@ -25926,7 +25082,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>293</v>
+        <v>29</v>
       </c>
       <c r="C294">
         <v>1123</v>
@@ -26009,7 +25165,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>294</v>
+        <v>29</v>
       </c>
       <c r="C295">
         <v>660</v>
@@ -26092,7 +25248,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>295</v>
+        <v>29</v>
       </c>
       <c r="C296">
         <v>1248</v>
@@ -26175,7 +25331,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>296</v>
+        <v>29</v>
       </c>
       <c r="C297">
         <v>1104</v>
@@ -26258,7 +25414,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>297</v>
+        <v>29</v>
       </c>
       <c r="C298">
         <v>1200</v>
@@ -26341,7 +25497,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>298</v>
+        <v>29</v>
       </c>
       <c r="C299">
         <v>1023</v>
@@ -26424,7 +25580,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>299</v>
+        <v>29</v>
       </c>
       <c r="C300">
         <v>734</v>
@@ -26507,7 +25663,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>300</v>
+        <v>29</v>
       </c>
       <c r="C301">
         <v>1207</v>
@@ -26590,7 +25746,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>301</v>
+        <v>29</v>
       </c>
       <c r="C302">
         <v>660</v>
@@ -26673,7 +25829,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>302</v>
+        <v>29</v>
       </c>
       <c r="C303">
         <v>714</v>
@@ -26756,7 +25912,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>303</v>
+        <v>29</v>
       </c>
       <c r="C304">
         <v>1232</v>
@@ -26839,7 +25995,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>304</v>
+        <v>29</v>
       </c>
       <c r="C305">
         <v>896</v>
@@ -26922,7 +26078,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>305</v>
+        <v>29</v>
       </c>
       <c r="C306">
         <v>720</v>
@@ -27005,7 +26161,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>306</v>
+        <v>29</v>
       </c>
       <c r="C307">
         <v>1232</v>
@@ -27088,7 +26244,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>307</v>
+        <v>29</v>
       </c>
       <c r="C308">
         <v>656</v>
@@ -27171,7 +26327,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>308</v>
+        <v>29</v>
       </c>
       <c r="C309">
         <v>1229</v>
@@ -27254,7 +26410,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>309</v>
+        <v>29</v>
       </c>
       <c r="C310">
         <v>635</v>
@@ -27337,7 +26493,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>310</v>
+        <v>29</v>
       </c>
       <c r="C311">
         <v>654</v>
@@ -27420,7 +26576,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>311</v>
+        <v>29</v>
       </c>
       <c r="C312">
         <v>1224</v>
@@ -27503,7 +26659,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>312</v>
+        <v>29</v>
       </c>
       <c r="C313">
         <v>1177</v>
@@ -27586,7 +26742,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>313</v>
+        <v>29</v>
       </c>
       <c r="C314">
         <v>1198</v>
@@ -27669,7 +26825,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>314</v>
+        <v>29</v>
       </c>
       <c r="C315">
         <v>900</v>
@@ -27752,7 +26908,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>315</v>
+        <v>29</v>
       </c>
       <c r="C316">
         <v>660</v>
@@ -27835,7 +26991,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>316</v>
+        <v>29</v>
       </c>
       <c r="C317">
         <v>778</v>
@@ -27918,7 +27074,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>317</v>
+        <v>29</v>
       </c>
       <c r="C318">
         <v>1247</v>
@@ -28001,7 +27157,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>318</v>
+        <v>29</v>
       </c>
       <c r="C319">
         <v>1221</v>
@@ -28084,7 +27240,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>319</v>
+        <v>29</v>
       </c>
       <c r="C320">
         <v>1242</v>
@@ -28167,7 +27323,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>320</v>
+        <v>29</v>
       </c>
       <c r="C321">
         <v>780</v>
@@ -28250,7 +27406,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>321</v>
+        <v>29</v>
       </c>
       <c r="C322">
         <v>1126</v>
@@ -28333,7 +27489,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>322</v>
+        <v>29</v>
       </c>
       <c r="C323">
         <v>1246</v>
@@ -28416,7 +27572,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>323</v>
+        <v>29</v>
       </c>
       <c r="C324">
         <v>1071</v>
@@ -28499,7 +27655,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>324</v>
+        <v>29</v>
       </c>
       <c r="C325">
         <v>1094</v>
@@ -28582,7 +27738,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>325</v>
+        <v>29</v>
       </c>
       <c r="C326">
         <v>1069</v>
@@ -28665,7 +27821,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>326</v>
+        <v>29</v>
       </c>
       <c r="C327">
         <v>1052</v>
@@ -28748,7 +27904,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>327</v>
+        <v>29</v>
       </c>
       <c r="C328">
         <v>1078</v>
@@ -28831,7 +27987,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>328</v>
+        <v>29</v>
       </c>
       <c r="C329">
         <v>666</v>
@@ -28914,7 +28070,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>329</v>
+        <v>29</v>
       </c>
       <c r="C330">
         <v>696</v>
@@ -28997,7 +28153,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>330</v>
+        <v>29</v>
       </c>
       <c r="C331">
         <v>1195</v>
@@ -29080,7 +28236,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>331</v>
+        <v>29</v>
       </c>
       <c r="C332">
         <v>1196</v>
@@ -29163,7 +28319,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>332</v>
+        <v>29</v>
       </c>
       <c r="C333">
         <v>1063</v>
@@ -29246,7 +28402,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>333</v>
+        <v>29</v>
       </c>
       <c r="C334">
         <v>1046</v>
@@ -29329,7 +28485,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>334</v>
+        <v>29</v>
       </c>
       <c r="C335">
         <v>1230</v>
@@ -29412,7 +28568,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>335</v>
+        <v>29</v>
       </c>
       <c r="C336">
         <v>1229</v>
@@ -29495,7 +28651,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>336</v>
+        <v>29</v>
       </c>
       <c r="C337">
         <v>962</v>
@@ -29578,7 +28734,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>337</v>
+        <v>29</v>
       </c>
       <c r="C338">
         <v>1093</v>
@@ -29661,7 +28817,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>338</v>
+        <v>29</v>
       </c>
       <c r="C339">
         <v>1076</v>
@@ -29744,7 +28900,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>339</v>
+        <v>29</v>
       </c>
       <c r="C340">
         <v>1034</v>
@@ -29827,7 +28983,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>340</v>
+        <v>29</v>
       </c>
       <c r="C341">
         <v>1147</v>
@@ -29910,7 +29066,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>341</v>
+        <v>29</v>
       </c>
       <c r="C342">
         <v>1002</v>
@@ -29993,7 +29149,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>342</v>
+        <v>29</v>
       </c>
       <c r="C343">
         <v>977</v>
@@ -30076,7 +29232,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>343</v>
+        <v>29</v>
       </c>
       <c r="C344">
         <v>999</v>
@@ -30159,7 +29315,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>344</v>
+        <v>29</v>
       </c>
       <c r="C345">
         <v>1050</v>
@@ -30242,7 +29398,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>345</v>
+        <v>29</v>
       </c>
       <c r="C346">
         <v>978</v>
@@ -30325,7 +29481,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>346</v>
+        <v>29</v>
       </c>
       <c r="C347">
         <v>1025</v>
@@ -30408,7 +29564,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>347</v>
+        <v>31</v>
       </c>
       <c r="C348">
         <v>977</v>
@@ -30491,7 +29647,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>348</v>
+        <v>32</v>
       </c>
       <c r="C349">
         <v>1028</v>
@@ -30574,7 +29730,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>349</v>
+        <v>33</v>
       </c>
       <c r="C350">
         <v>1066</v>
@@ -30657,7 +29813,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>350</v>
+        <v>34</v>
       </c>
       <c r="C351">
         <v>928</v>
@@ -30740,7 +29896,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>351</v>
+        <v>35</v>
       </c>
       <c r="C352">
         <v>979</v>
@@ -30823,7 +29979,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="C353">
         <v>1243</v>
@@ -30906,7 +30062,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>353</v>
+        <v>37</v>
       </c>
       <c r="C354">
         <v>1177</v>
@@ -30989,7 +30145,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>354</v>
+        <v>38</v>
       </c>
       <c r="C355">
         <v>1214</v>
@@ -31072,7 +30228,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>355</v>
+        <v>39</v>
       </c>
       <c r="C356">
         <v>1204</v>
@@ -31155,7 +30311,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>356</v>
+        <v>40</v>
       </c>
       <c r="C357">
         <v>1195</v>
@@ -31238,7 +30394,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>357</v>
+        <v>41</v>
       </c>
       <c r="C358">
         <v>1090</v>
@@ -31321,7 +30477,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>358</v>
+        <v>42</v>
       </c>
       <c r="C359">
         <v>1133</v>
@@ -31404,7 +30560,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>359</v>
+        <v>43</v>
       </c>
       <c r="C360">
         <v>1066</v>
@@ -31487,7 +30643,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>360</v>
+        <v>44</v>
       </c>
       <c r="C361">
         <v>654</v>
@@ -31570,7 +30726,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>361</v>
+        <v>45</v>
       </c>
       <c r="C362">
         <v>987</v>
@@ -31653,7 +30809,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>362</v>
+        <v>46</v>
       </c>
       <c r="C363">
         <v>1219</v>
@@ -31736,7 +30892,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>363</v>
+        <v>47</v>
       </c>
       <c r="C364">
         <v>1074</v>
@@ -31819,7 +30975,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>364</v>
+        <v>48</v>
       </c>
       <c r="C365">
         <v>1248</v>
@@ -31902,7 +31058,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>365</v>
+        <v>49</v>
       </c>
       <c r="C366">
         <v>1046</v>
@@ -31985,7 +31141,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>366</v>
+        <v>50</v>
       </c>
       <c r="C367">
         <v>1048</v>
@@ -32068,7 +31224,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>367</v>
+        <v>51</v>
       </c>
       <c r="C368">
         <v>1025</v>
@@ -32151,7 +31307,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>368</v>
+        <v>52</v>
       </c>
       <c r="C369">
         <v>833</v>
@@ -32234,7 +31390,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>369</v>
+        <v>53</v>
       </c>
       <c r="C370">
         <v>917</v>
@@ -32317,7 +31473,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>370</v>
+        <v>54</v>
       </c>
       <c r="C371">
         <v>1217</v>
@@ -32400,7 +31556,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>371</v>
+        <v>55</v>
       </c>
       <c r="C372">
         <v>1041</v>
@@ -32483,7 +31639,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>372</v>
+        <v>56</v>
       </c>
       <c r="C373">
         <v>1115</v>
@@ -32566,7 +31722,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>373</v>
+        <v>57</v>
       </c>
       <c r="C374">
         <v>1012</v>
@@ -32649,7 +31805,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>374</v>
+        <v>58</v>
       </c>
       <c r="C375">
         <v>1085</v>
@@ -32732,7 +31888,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>375</v>
+        <v>59</v>
       </c>
       <c r="C376">
         <v>936</v>
@@ -32815,7 +31971,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>376</v>
+        <v>60</v>
       </c>
       <c r="C377">
         <v>719</v>
@@ -32898,7 +32054,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>377</v>
+        <v>61</v>
       </c>
       <c r="C378">
         <v>1253</v>
@@ -32981,7 +32137,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>378</v>
+        <v>62</v>
       </c>
       <c r="C379">
         <v>1078</v>
@@ -33064,7 +32220,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>379</v>
+        <v>63</v>
       </c>
       <c r="C380">
         <v>1246</v>
@@ -33147,7 +32303,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>380</v>
+        <v>64</v>
       </c>
       <c r="C381">
         <v>1205</v>
@@ -33230,7 +32386,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>381</v>
+        <v>65</v>
       </c>
       <c r="C382">
         <v>1116</v>
@@ -33313,7 +32469,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>382</v>
+        <v>66</v>
       </c>
       <c r="C383">
         <v>772</v>
@@ -33396,7 +32552,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>383</v>
+        <v>67</v>
       </c>
       <c r="C384">
         <v>1243</v>
@@ -33479,7 +32635,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>384</v>
+        <v>68</v>
       </c>
       <c r="C385">
         <v>1149</v>
@@ -33562,7 +32718,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>385</v>
+        <v>69</v>
       </c>
       <c r="C386">
         <v>1181</v>
@@ -33645,7 +32801,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>386</v>
+        <v>70</v>
       </c>
       <c r="C387">
         <v>1120</v>
@@ -33728,7 +32884,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>387</v>
+        <v>71</v>
       </c>
       <c r="C388">
         <v>1081</v>
@@ -33811,7 +32967,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>388</v>
+        <v>72</v>
       </c>
       <c r="C389">
         <v>1125</v>
@@ -33894,7 +33050,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>389</v>
+        <v>73</v>
       </c>
       <c r="C390">
         <v>718</v>
@@ -33977,7 +33133,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>390</v>
+        <v>74</v>
       </c>
       <c r="C391">
         <v>1239</v>
@@ -34060,7 +33216,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>391</v>
+        <v>75</v>
       </c>
       <c r="C392">
         <v>1228</v>
@@ -34143,7 +33299,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>392</v>
+        <v>76</v>
       </c>
       <c r="C393">
         <v>1233</v>
@@ -34226,7 +33382,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>393</v>
+        <v>77</v>
       </c>
       <c r="C394">
         <v>1236</v>
@@ -34309,7 +33465,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>394</v>
+        <v>78</v>
       </c>
       <c r="C395">
         <v>1164</v>
@@ -34392,7 +33548,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="C396">
         <v>1135</v>
@@ -34475,7 +33631,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>396</v>
+        <v>80</v>
       </c>
       <c r="C397">
         <v>1198</v>
@@ -34558,7 +33714,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>397</v>
+        <v>81</v>
       </c>
       <c r="C398">
         <v>1109</v>
@@ -34641,7 +33797,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="C399">
         <v>1174</v>
@@ -34724,7 +33880,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>399</v>
+        <v>83</v>
       </c>
       <c r="C400">
         <v>1164</v>
@@ -34807,7 +33963,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="C401">
         <v>1093</v>
@@ -34890,7 +34046,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>401</v>
+        <v>85</v>
       </c>
       <c r="C402">
         <v>1084</v>
@@ -34973,7 +34129,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>402</v>
+        <v>86</v>
       </c>
       <c r="C403">
         <v>1165</v>
@@ -35056,7 +34212,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>403</v>
+        <v>87</v>
       </c>
       <c r="C404">
         <v>714</v>
@@ -35139,7 +34295,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>404</v>
+        <v>88</v>
       </c>
       <c r="C405">
         <v>1220</v>
@@ -35222,7 +34378,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>405</v>
+        <v>89</v>
       </c>
       <c r="C406">
         <v>1218</v>
@@ -35305,7 +34461,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>406</v>
+        <v>90</v>
       </c>
       <c r="C407">
         <v>1228</v>
@@ -35388,7 +34544,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>407</v>
+        <v>91</v>
       </c>
       <c r="C408">
         <v>1144</v>
@@ -35471,7 +34627,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>408</v>
+        <v>92</v>
       </c>
       <c r="C409">
         <v>1211</v>
@@ -35554,7 +34710,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>409</v>
+        <v>93</v>
       </c>
       <c r="C410">
         <v>990</v>
@@ -35637,7 +34793,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>410</v>
+        <v>94</v>
       </c>
       <c r="C411">
         <v>1189</v>
@@ -35720,7 +34876,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>411</v>
+        <v>95</v>
       </c>
       <c r="C412">
         <v>906</v>
@@ -35803,7 +34959,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="C413">
         <v>1197</v>
@@ -35886,7 +35042,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>413</v>
+        <v>97</v>
       </c>
       <c r="C414">
         <v>594</v>
@@ -35969,7 +35125,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>414</v>
+        <v>98</v>
       </c>
       <c r="C415">
         <v>728</v>
@@ -36052,7 +35208,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>415</v>
+        <v>99</v>
       </c>
       <c r="C416">
         <v>1081</v>
@@ -36135,7 +35291,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>416</v>
+        <v>100</v>
       </c>
       <c r="C417">
         <v>966</v>
@@ -36218,7 +35374,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>417</v>
+        <v>101</v>
       </c>
       <c r="C418">
         <v>1120</v>
@@ -36301,7 +35457,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>418</v>
+        <v>102</v>
       </c>
       <c r="C419">
         <v>1026</v>
@@ -36384,7 +35540,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>419</v>
+        <v>103</v>
       </c>
       <c r="C420">
         <v>1240</v>
